--- a/04_DESIGN_TABLES/DesignTable_6400L.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6400L.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -592,7 +592,11 @@
           <t>Air-Way s90 only (double-pass 15 rows); JIC end VERIFIED (MS33656J); ORB groove from measured set (all dashes covered)</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L6@DRIVE=2.08~2.080; C4HEX@HEX=0.56~0.562</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -768,7 +772,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -776,7 +780,11 @@
           <t>Air-Way s90 only (double-pass 15 rows); JIC end VERIFIED (MS33656J); ORB groove from measured set (all dashes covered)</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L6@DRIVE=2.31~2.310; C4HEX@HEX=0.69~0.688</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -891,7 +899,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -899,7 +907,11 @@
           <t>Air-Way s90 only (double-pass 15 rows); JIC end VERIFIED (MS33656J); ORB groove from measured set (all dashes covered)</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L6@DRIVE=2.7~2.700; C4HEX@HEX=0.88~0.875</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1075,7 +1087,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1083,7 +1095,11 @@
           <t>Air-Way s90 only (double-pass 15 rows); JIC end VERIFIED (MS33656J); ORB groove from measured set (all dashes covered)</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L6@DRIVE=3.04~3.040; C4HEX@HEX=1~1.000</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1259,7 +1275,7 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1267,7 +1283,11 @@
           <t>Air-Way s90 only (double-pass 15 rows); JIC end VERIFIED (MS33656J); ORB groove from measured set (all dashes covered)</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L6@DRIVE=3.61~3.610; C4HEX@HEX=1.25~1.250</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1321,7 +1341,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1329,7 +1349,11 @@
           <t>Air-Way s90 only (double-pass 15 rows); JIC end VERIFIED (MS33656J); ORB groove from measured set (all dashes covered)</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L6@DRIVE=3.98~3.980; C4HEX@HEX=1.5~1.500</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>BUILD</t>
